--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI5"/>
+  <dimension ref="A1:BI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,203 +1336,408 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FS6801-L-08-08-NWO-FG</t>
+          <t>FS6801-16-20-NWO-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.1</v>
+        <v>1.76</v>
       </c>
       <c r="C5" t="n">
-        <v>0.375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.40625</v>
+        <v>0.71875</v>
       </c>
       <c r="E5" t="n">
-        <v>0.45725</v>
+        <v>0.62675</v>
       </c>
       <c r="F5" t="n">
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3595</v>
+        <v>0.6565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3145</v>
+        <v>0.5335</v>
       </c>
       <c r="I5" t="n">
         <v>0.052</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2125</v>
+        <v>0.4315</v>
       </c>
       <c r="K5" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0.375</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.91</v>
+        <v>1.087</v>
       </c>
       <c r="N5" t="n">
-        <v>0.039</v>
+        <v>0.043</v>
       </c>
       <c r="O5" t="n">
-        <v>0.475</v>
+        <v>0.945</v>
       </c>
       <c r="P5" t="n">
         <v>75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.55271</v>
+        <v>1.09542</v>
       </c>
       <c r="R5" t="n">
         <v>75</v>
       </c>
       <c r="S5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.0825</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.071</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.47004</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.94058</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>FS6801-16-20-NWO-FG</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow, 1 7/16-12 UN (male O-ring face seal, SAE J1453) x 1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>FS6801</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1 7/16-12 UN (male O-ring face seal, SAE J1453)</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (adjustable male ORB)</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-16-20-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-16-20 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>forged (-FG): Air-Way non-forged FF6801-16-20 NWO = Brennan forged FS6801-16-20-NWO-FG p10 on every compared cell (M LGTH ~ L7, N LGTH ~ L10, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801 is used only where Brennan FS6801-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5660 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.73 = L10 - L11 (Air-Way), thread 0.546 = stud - undercut 0.184, tip -&gt; body face 1.363 (FS lock nut 0.54 thick, NWO_FS)</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>FS6801-16-20-NWO-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FS6801-L-08-08-NWO-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="P6" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.55271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>75</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.41</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>0.475</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>0.505</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V6" t="n">
         <v>0.041</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W6" t="n">
         <v>0.33</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="X6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.404</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z6" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA6" t="n">
         <v>0.41</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB6" t="n">
         <v>0.37</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC6" t="n">
         <v>1.1</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD6" t="n">
         <v>0.39</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE6" t="n">
         <v>2.95</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF6" t="n">
         <v>0.8125</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG6" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH6" t="n">
         <v>0.45725</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI6" t="n">
         <v>0.03383</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ6" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK6" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL6" t="n">
         <v>0.75</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM6" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN6" t="n">
         <v>0.404</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO6" t="n">
         <v>0.03383</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP6" t="n">
         <v>0.01562</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ6" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR6" t="n">
         <v>0.75</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS6" t="n">
         <v>0.596</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AT6" t="n">
         <v>0.75</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU6" t="n">
         <v>1.91</v>
       </c>
-      <c r="AV5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AV6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AX6" t="n">
         <v>0.21601</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AY6" t="n">
         <v>0.21601</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AZ6" t="n">
         <v>0.43251</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>FS6801-L-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>ORFS 90 deg Male Face Seal x Adjustable Male ORB Elbow, 13/16-16 UN (male O-ring face seal, SAE J1453) x 3/4-16 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>FS6801</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>13/16-16 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>3/4-16 (adjustable male ORB)</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>Air-Way FF6801-L (s26, double-pass 2026-10-15, parts.air-way.com/api/series/26, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6801-L-08-08-NWO-FG (ORFS-p009-t04); FORGED part: Air-Way NON-forged row FF6801-L-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | FOLD: FS6801-L fold: the forged hex arm of the adjustable-stud leg runs on to the longer stud leg L50 (washer face L51); stud, lock nut and face-seal leg as FS6801 (Brennan FS6801-L-08-08-NWO-FG STEP vs FS6801-08-08-NWO-FG; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>forged (-FG): Air-Way non-forged FF6801-L-8-8 NWO = Brennan forged FS6801-L-08-08-NWO-FG p9 on every compared cell (M LGTH ~ L7, N LGTH ~ L50, C HEX ~ S3, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6801-L is used only where Brennan FS6801-L-NWO-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5667 (no dimensions) | FS6801-L row folded into the FS6801 master: Brennan FS6801-L-08-08-NWO-FG STEP shows the stud leg's forged hex arm simply running longer (tip -&gt; washer face 0.540 and the face-seal leg 1.118 as on FS6801-08-08; Q-FS-MASTER, user 2026-10-18) | DataStatus VERIFIED -&gt; ASSUMED: the adjustable ORB nut/washer/neck geometry is single-source (Brennan 6801-XX-XX-NWO-FG STEPs) | leg 2: adjustable stud tip -&gt; washer face 0.55 = L10 - L11 (Air-Way), thread 0.404 = stud - undercut 0.146, tip -&gt; body face 1.04 (FS lock nut 0.41 thick, NWO_FS)</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>FS6801-L-08-08-NWO-FG</t>
         </is>

--- a/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801_SW2.xlsx
+++ b/tools/_out/groupB_20261021/out/fs/DesignTable_FS6801_SW2.xlsx
@@ -909,7 +909,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-08-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-04-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-4-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-04-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-4-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-06-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-6-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-06-08-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-6-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-16-20-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-16-20 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801 (s25, double-pass 2026-10-15, parts.air-way.com/api/series/25, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p10 FS6801-16-20-NWO-FG (ORFS-p010-t02); FORGED part: Air-Way NON-forged row FF6801-16-20 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>Air-Way FF6801-L (s26, double-pass 2026-10-15, parts.air-way.com/api/series/26, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6801-L-08-08-NWO-FG (ORFS-p009-t04); FORGED part: Air-Way NON-forged row FF6801-L-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | FOLD: FS6801-L fold: the forged hex arm of the adjustable-stud leg runs on to the longer stud leg L50 (washer face L51); stud, lock nut and face-seal leg as FS6801 (Brennan FS6801-L-08-08-NWO-FG STEP vs FS6801-08-08-NWO-FG; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6801-L (s26, double-pass 2026-10-15, parts.air-way.com/api/series/26, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6801-L-08-08-NWO-FG (ORFS-p009-t04); FORGED part: Air-Way NON-forged row FF6801-L-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | FOLD: FS6801-L fold: the forged hex arm of the adjustable-stud leg runs on to the longer stud leg L50 (washer face L51); stud, lock nut and face-seal leg as FS6801 (Brennan FS6801-L-08-08-NWO-FG STEP vs FS6801-08-08-NWO-FG; measured at -08-08 only) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the Brennan FS6801-NN-NN-NWO-FG of the size (NWO_FS -04 ... -24; -08: washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
